--- a/Frezyderm.xlsx
+++ b/Frezyderm.xlsx
@@ -2343,7 +2343,6 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="115.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="6.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="57.21"/>
   </cols>
   <sheetData>
